--- a/code/data/numbers/lcdm-free.xlsx
+++ b/code/data/numbers/lcdm-free.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/852b2bada49559ee/code_final/data/numbers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28943\OneDrive\NeutrinoForecast_J-PAS_PFS\code\data\numbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_085D38BF95627E0F6235547658AC46F99AE18372" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B31E2E8-D05D-4C44-BFEE-38124897D290}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BF7E4A-2C02-4716-9846-DB5A09BB6081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="18720" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="437" windowWidth="18720" windowHeight="11434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -153,10 +158,10 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -463,9 +468,8 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.61328125" customWidth="1"/>
     <col min="2" max="3" width="9.23046875" style="3"/>
-    <col min="4" max="4" width="9.23046875" style="6"/>
+    <col min="4" max="4" width="9.23046875" style="5"/>
     <col min="5" max="6" width="9.23046875" style="3"/>
     <col min="7" max="8" width="9.23046875" style="7"/>
   </cols>
@@ -486,10 +490,10 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -498,25 +502,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="3">
-        <v>7.8274464510318994E-3</v>
+        <v>7.9322408974910399E-3</v>
       </c>
       <c r="C2" s="3">
-        <v>9.3925305975702308E-3</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1.095946669881891E-3</v>
+        <v>9.2647579890232108E-3</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.099538416981777E-3</v>
       </c>
       <c r="E2" s="3">
-        <v>1.1036353030355141E-2</v>
+        <v>1.1240859735186241E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>3.2954891139405072E-3</v>
+        <v>3.3055210737813448E-3</v>
       </c>
       <c r="G2" s="7">
-        <v>5.2012638186082982E-2</v>
+        <v>5.1426481115197431E-2</v>
       </c>
       <c r="H2" s="7">
-        <v>4.8054431950656541E-2</v>
+        <v>4.8278622397917893E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -524,25 +528,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="3">
-        <v>1.9821177648566619E-2</v>
+        <v>1.9821177648566678E-2</v>
       </c>
       <c r="C3" s="3">
-        <v>1.5170900388095831E-2</v>
-      </c>
-      <c r="D3" s="6">
-        <v>5.7204595804714103E-3</v>
+        <v>1.517090038809582E-2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5.7204595804713002E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>3.4881480960916228E-2</v>
+        <v>3.4881480960916297E-2</v>
       </c>
       <c r="F3" s="3">
         <v>2.637521422830363E-2</v>
       </c>
       <c r="G3" s="7">
-        <v>0.41316854861122199</v>
+        <v>0.41316854861121832</v>
       </c>
       <c r="H3" s="7">
-        <v>0.74487796082864621</v>
+        <v>0.74487796082869129</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -555,7 +559,7 @@
       <c r="C4" s="3">
         <v>2.8294867875278039E-2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8.9533166640331265E-3</v>
       </c>
       <c r="E4" s="3">
@@ -576,25 +580,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="3">
-        <v>4.569420626475932E-2</v>
+        <v>4.5694206264759382E-2</v>
       </c>
       <c r="C5" s="3">
-        <v>3.4549741729820067E-2</v>
-      </c>
-      <c r="D5" s="6">
-        <v>9.1911770493651856E-3</v>
+        <v>3.4549741729820352E-2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9.1911770493651821E-3</v>
       </c>
       <c r="E5" s="3">
-        <v>8.3358611305324834E-2</v>
+        <v>8.3358611305324931E-2</v>
       </c>
       <c r="F5" s="3">
-        <v>6.8013551016574927E-2</v>
+        <v>6.8013551016575274E-2</v>
       </c>
       <c r="G5" s="7">
-        <v>0.72786543853491803</v>
+        <v>0.72786543853492691</v>
       </c>
       <c r="H5" s="7">
-        <v>2.344445288450332</v>
+        <v>2.344445288450367</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -602,25 +606,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>3.4885185037585073E-2</v>
+        <v>3.4885185037585267E-2</v>
       </c>
       <c r="C6" s="3">
-        <v>1.569208620847681E-2</v>
-      </c>
-      <c r="D6" s="6">
-        <v>6.3589255488093431E-3</v>
+        <v>1.5692086208476841E-2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6.358925548809344E-3</v>
       </c>
       <c r="E6" s="3">
-        <v>6.6767524865699965E-2</v>
+        <v>6.6767524865699784E-2</v>
       </c>
       <c r="F6" s="3">
-        <v>6.5194442756714738E-2</v>
+        <v>6.5194442756714654E-2</v>
       </c>
       <c r="G6" s="7">
-        <v>0.6726887092121494</v>
+        <v>0.67268870921215163</v>
       </c>
       <c r="H6" s="7">
-        <v>1.7694377546596911</v>
+        <v>1.769437754659684</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -628,25 +632,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="3">
-        <v>1.276491371602443E-2</v>
+        <v>1.276491371602414E-2</v>
       </c>
       <c r="C7" s="3">
-        <v>8.3929823901560275E-3</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3.399660168734101E-3</v>
+        <v>8.3929823901562183E-3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3.3996601687340099E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>2.5124326024114671E-2</v>
+        <v>2.5124326024112499E-2</v>
       </c>
       <c r="F7" s="3">
-        <v>1.608588270540285E-2</v>
+        <v>1.608588270540166E-2</v>
       </c>
       <c r="G7" s="7">
-        <v>0.29705686823309252</v>
+        <v>0.29705686823306821</v>
       </c>
       <c r="H7" s="7">
-        <v>0.5854920693871738</v>
+        <v>0.58549206938711418</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -654,25 +658,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>1.153562259617593E-2</v>
+        <v>1.1535622596176069E-2</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0073373712867806E-3</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2.7194128113152511E-3</v>
+        <v>6.0073373712870286E-3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.7194128113139479E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>2.3100460874572661E-2</v>
+        <v>2.3100460874571498E-2</v>
       </c>
       <c r="F8" s="3">
-        <v>1.2538113561892231E-2</v>
+        <v>1.2538113561887601E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>0.26911798301142448</v>
+        <v>0.26911798301140222</v>
       </c>
       <c r="H8" s="7">
-        <v>0.53167787807645117</v>
+        <v>0.5316778780764343</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -680,25 +684,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="3">
-        <v>8.0036761596973711E-3</v>
+        <v>8.0036761596973226E-3</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6189932087712503E-3</v>
-      </c>
-      <c r="D9" s="6">
-        <v>2.5254393002941359E-3</v>
+        <v>4.6189932087712321E-3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2.525439300294119E-3</v>
       </c>
       <c r="E9" s="3">
-        <v>1.7475035642890831E-2</v>
+        <v>1.7475035642890661E-2</v>
       </c>
       <c r="F9" s="3">
-        <v>2.0677566562496062E-2</v>
+        <v>2.067756656249611E-2</v>
       </c>
       <c r="G9" s="7">
-        <v>0.22772194220832689</v>
+        <v>0.2277219422083282</v>
       </c>
       <c r="H9" s="7">
-        <v>0.4132432148099579</v>
+        <v>0.41324321480995302</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -706,25 +710,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="3">
-        <v>2.1219523869389881E-3</v>
+        <v>2.1394596269079511E-3</v>
       </c>
       <c r="C10" s="3">
-        <v>2.1007588639771822E-3</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2.8321974956370188E-4</v>
+        <v>2.086641793773894E-3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2.8492592228642648E-4</v>
       </c>
       <c r="E10" s="3">
-        <v>3.986251912061858E-3</v>
+        <v>4.055280788954542E-3</v>
       </c>
       <c r="F10" s="3">
-        <v>2.0681018593028261E-3</v>
+        <v>2.0431185097378661E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>1.7325511554144239E-2</v>
+        <v>1.7183821912067038E-2</v>
       </c>
       <c r="H10" s="7">
-        <v>3.4213623379275311E-2</v>
+        <v>3.3876295435116853E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -732,25 +736,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="3">
-        <v>1.644444843479313E-3</v>
+        <v>1.654478236753952E-3</v>
       </c>
       <c r="C11" s="3">
-        <v>1.94159110332096E-3</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2.189883531817056E-4</v>
+        <v>1.928912900421011E-3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2.1962796403265971E-4</v>
       </c>
       <c r="E11" s="3">
-        <v>3.0191516226745429E-3</v>
+        <v>3.062972181795077E-3</v>
       </c>
       <c r="F11" s="3">
-        <v>1.9408831711597201E-3</v>
+        <v>1.9175075449366489E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>1.3931212850079139E-2</v>
+        <v>1.3786614089013721E-2</v>
       </c>
       <c r="H11" s="7">
-        <v>3.165412709285572E-2</v>
+        <v>3.1526708695523792E-2</v>
       </c>
     </row>
   </sheetData>
